--- a/elenco.xlsx
+++ b/elenco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\REPO\Dictionary-Italian-Translation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09705B28-5966-427A-ABE3-8C1911E7DBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AD47B2-038C-4EF8-952B-6E58EE76CCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{135624D2-5429-40FB-8D36-4751D93DBFED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{135624D2-5429-40FB-8D36-4751D93DBFED}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="746">
   <si>
     <t>blades-in-the-dark</t>
   </si>
@@ -197,9 +197,6 @@
     <t>vaesen</t>
   </si>
   <si>
-    <t>vtm5e</t>
-  </si>
-  <si>
     <t>whtow</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>yzecoriolis</t>
   </si>
   <si>
-    <t>aa-autorec</t>
-  </si>
-  <si>
     <t>about-face</t>
   </si>
   <si>
@@ -236,9 +230,6 @@
     <t>aime</t>
   </si>
   <si>
-    <t>alienrpg-corerules</t>
-  </si>
-  <si>
     <t>always-hp</t>
   </si>
   <si>
@@ -290,9 +281,6 @@
     <t>combat-utility-belt</t>
   </si>
   <si>
-    <t>compact-scene-navigation</t>
-  </si>
-  <si>
     <t>compendium-browser</t>
   </si>
   <si>
@@ -332,9 +320,6 @@
     <t>dice-so-nice</t>
   </si>
   <si>
-    <t>dnd5e-system-customizer</t>
-  </si>
-  <si>
     <t>dragonbane-item-browser</t>
   </si>
   <si>
@@ -359,9 +344,6 @@
     <t>enhanced-terrain-layer</t>
   </si>
   <si>
-    <t>epic-rolls-5e</t>
-  </si>
-  <si>
     <t>farchievements</t>
   </si>
   <si>
@@ -377,21 +359,12 @@
     <t>forien-scene-navigator</t>
   </si>
   <si>
-    <t>fvtt-paper-doll-ui</t>
-  </si>
-  <si>
     <t>fvtt-party-resources</t>
   </si>
   <si>
-    <t>fvtt-youtube-player</t>
-  </si>
-  <si>
     <t>fxmaster</t>
   </si>
   <si>
-    <t>gatherer</t>
-  </si>
-  <si>
     <t>hand-mini-bar</t>
   </si>
   <si>
@@ -401,9 +374,6 @@
     <t>health-monitor</t>
   </si>
   <si>
-    <t>hexplorer</t>
-  </si>
-  <si>
     <t>hot-pan</t>
   </si>
   <si>
@@ -437,9 +407,6 @@
     <t>masks-newgeneration-unofficial</t>
   </si>
   <si>
-    <t>mastercrafted</t>
-  </si>
-  <si>
     <t>merchant-sheet-npc</t>
   </si>
   <si>
@@ -488,9 +455,6 @@
     <t>multi-token-edit</t>
   </si>
   <si>
-    <t>party-monitor-dock</t>
-  </si>
-  <si>
     <t>patrol</t>
   </si>
   <si>
@@ -542,9 +506,6 @@
     <t>simple-dice-roller</t>
   </si>
   <si>
-    <t>simple-quest</t>
-  </si>
-  <si>
     <t>simple-weather</t>
   </si>
   <si>
@@ -566,12 +527,6 @@
     <t>terrain-ruler</t>
   </si>
   <si>
-    <t>three-actor-portrait</t>
-  </si>
-  <si>
-    <t>tidbits</t>
-  </si>
-  <si>
     <t>tidy5e-sheet</t>
   </si>
   <si>
@@ -596,9 +551,6 @@
     <t>token-auras</t>
   </si>
   <si>
-    <t>tokenflip</t>
-  </si>
-  <si>
     <t>token-hud-wildcard</t>
   </si>
   <si>
@@ -608,9 +560,6 @@
     <t>token-mold</t>
   </si>
   <si>
-    <t>token-notes</t>
-  </si>
-  <si>
     <t>turnmarker</t>
   </si>
   <si>
@@ -633,16 +582,1719 @@
   </si>
   <si>
     <t>yze-combat</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Progetto</t>
+  </si>
+  <si>
+    <t>Lingua</t>
+  </si>
+  <si>
+    <t>Warhammer Age of Sigmar : Soulbound</t>
+  </si>
+  <si>
+    <t>https://github.com/moo-man/AoS-Soulbound-FoundryVTT</t>
+  </si>
+  <si>
+    <t>https://github.com/moo-man/AoS-Soulbound-FoundryVTT/raw/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>AGE System (unofficial)</t>
+  </si>
+  <si>
+    <t>https://github.com/vkdolea/age-system/raw/refs/heads/workspace/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/vkdolea/age-system</t>
+  </si>
+  <si>
+    <t>Alien RPG System</t>
+  </si>
+  <si>
+    <t>https://github.com/pwatson100/alienrpg</t>
+  </si>
+  <si>
+    <t>13th Age</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/asacolips-projects/13th-age/refs/heads/main/src/languages/en.yaml</t>
+  </si>
+  <si>
+    <t>https://github.com/asacolips-projects/13th-age</t>
+  </si>
+  <si>
+    <t>Blades In The Dark</t>
+  </si>
+  <si>
+    <t>https://github.com/Dez384/foundryvtt-blades-in-the-dark</t>
+  </si>
+  <si>
+    <t>City of Mist</t>
+  </si>
+  <si>
+    <t>https://github.com/taragnor/city-of-mist</t>
+  </si>
+  <si>
+    <t>Call of Cthulhu 7th edition</t>
+  </si>
+  <si>
+    <t>https://github.com/Miskatonic-Investigative-Society/CoC7-FoundryVTT</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Miskatonic-Investigative-Society/CoC7-FoundryVTT/refs/heads/develop/static/lang/it.json</t>
+  </si>
+  <si>
+    <t>Coriolis: The Great Dark</t>
+  </si>
+  <si>
+    <t>https://github.com/hodpub/coriolis-tgd</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/hodpub/coriolis-tgd/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Cosmere Roleplaying Game</t>
+  </si>
+  <si>
+    <t>https://github.com/the-metalworks/cosmere-rpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/the-metalworks/cosmere-rpg/refs/heads/main/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Crucible</t>
+  </si>
+  <si>
+    <t>Mausritter</t>
+  </si>
+  <si>
+    <t>Mouseguard</t>
+  </si>
+  <si>
+    <t>https://github.com/foundryvtt/crucible</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/foundryvtt/crucible/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Cyberpunk RED</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/cyberpunk-red-team/fvtt-cyberpunk-red-core</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/cyberpunk-red-team/fvtt-cyberpunk-red-core/-/raw/dev/src/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>CY_BORG</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/cyborg-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/cyborg-foundry-vtt/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Dark Heresy 2E</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Vendare/DarkHeresy2E-FoundryVTT/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/Vendare/DarkHeresy2E-FoundryVTT</t>
+  </si>
+  <si>
+    <t>Dungeon Crawl Classics (DCC)</t>
+  </si>
+  <si>
+    <t>https://github.com/foundryvtt-dcc/dcc</t>
+  </si>
+  <si>
+    <t>Death in Space</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/deathinspace-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/deathinspace-foundry-vtt/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Delta Green: The Role-Playing Game</t>
+  </si>
+  <si>
+    <t>https://github.com/deltagreen-foundryvtt/delta-green-foundry-vtt-system</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/deltagreen-foundryvtt/delta-green-foundry-vtt-system/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Shadow of the Demon Lord</t>
+  </si>
+  <si>
+    <t>https://github.com/Xacus/demonlord</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Xacus/demonlord/refs/heads/master/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/pwatson100/alienrpg/raw/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/Dez384/foundryvtt-blades-in-the-dark/raw/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/taragnor/city-of-mist/raw/refs/heads/main/src/city-of-mist/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/foundryvtt-dcc/dcc/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Dishonored: The Roleplaying Game</t>
+  </si>
+  <si>
+    <t>https://github.com/Muttley/foundryvtt-dishonored</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Muttley/foundryvtt-dishonored/refs/heads/develop/i18n/it.yaml</t>
+  </si>
+  <si>
+    <t>https://github.com/pafvel/dragonbane</t>
+  </si>
+  <si>
+    <t>Dragonbane - Drakar och Demoner</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/pafvel/dragonbane/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Dune: Adventures in the Imperium</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/fvtt-modiphius/foundryvtt-dune-system/-/raw/master/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/fvtt-modiphius/foundryvtt-dune-system</t>
+  </si>
+  <si>
+    <t>Dungeon World</t>
+  </si>
+  <si>
+    <t>https://github.com/asacolips-projects/dungeonworld</t>
+  </si>
+  <si>
+    <t>https://github.com/asacolips-projects/dungeonworld/raw/refs/heads/main/src/yaml/lang/it.yml</t>
+  </si>
+  <si>
+    <t>Forbidden Lands</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/forbidden-lands-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/forbidden-lands-foundry-vtt/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Genesys Unofficial (Alpha)</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Mezryss/FVTT-Genesys/refs/heads/main/yaml/lang/en.yml</t>
+  </si>
+  <si>
+    <t>https://github.com/Mezryss/FVTT-Genesys</t>
+  </si>
+  <si>
+    <t>GURPS 4th Edition Game Aid (Unofficial)</t>
+  </si>
+  <si>
+    <t>https://github.com/crnormand/gurps</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/crnormand/gurps/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Index Card RPG</t>
+  </si>
+  <si>
+    <t>https://github.com/jessev14/FoundryVTT-ICRPG</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jessev14/FoundryVTT-ICRPG/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Warhammer 40,000 Roleplay: Imperium Maledictum</t>
+  </si>
+  <si>
+    <t>https://github.com/moo-man/ImpMal-FoundryVTT</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/moo-man/ImpMal-FoundryVTT/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>GUMSHOE</t>
+  </si>
+  <si>
+    <t>https://github.com/lumphammer/gumshoe-fvtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/lumphammer/gumshoe-fvtt/refs/heads/main/public/lang/en.json</t>
+  </si>
+  <si>
+    <t>Ironsworn &amp; Starforged</t>
+  </si>
+  <si>
+    <t>https://github.com/ben/foundry-ironsworn</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ben/foundry-ironsworn/refs/heads/main/system/lang/en.json</t>
+  </si>
+  <si>
+    <t>Legend of the Five Rings (5th Edition)</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/teaml5r/l5r5e</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/teaml5r/l5r5e/-/raw/master/system/lang/it-it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>File Lingua</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>LANCER</t>
+  </si>
+  <si>
+    <t>https://github.com/Eranziel/foundryvtt-lancer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Eranziel/foundryvtt-lancer/refs/heads/master/public/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/Futil/foundry-mausritter</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Futil/foundry-mausritter/refs/heads/v10/lang/en.json</t>
+  </si>
+  <si>
+    <t>MoSh - Unofficial Mothership</t>
+  </si>
+  <si>
+    <t>https://github.com/Futil/foundry-mothership</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Futil/foundry-mothership/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/jsavko/mouseguard</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jsavko/mouseguard/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Mutant Year Zero</t>
+  </si>
+  <si>
+    <t>https://github.com/superseva/mutant-year-zero</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/superseva/mutant-year-zero/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Old-School Essentials</t>
+  </si>
+  <si>
+    <t>https://github.com/NecroticGnome/ose-foundry-core</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/NecroticGnome/ose-foundry-core/refs/heads/main/src/lang/it.json</t>
+  </si>
+  <si>
+    <t>Powered by the Apocalypse</t>
+  </si>
+  <si>
+    <t>https://github.com/asacolips-projects/pbta</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/asacolips-projects/pbta/refs/heads/main/src/yaml/lang/pt-br.yml</t>
+  </si>
+  <si>
+    <t>pt-br</t>
+  </si>
+  <si>
+    <t>Pathfinder 1</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundryvtt_pathfinder1e/foundryvtt-pathfinder1</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundryvtt_pathfinder1e/foundryvtt-pathfinder1/-/raw/master/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>pf2e</t>
+  </si>
+  <si>
+    <t>https://github.com/foundryvtt/pf2e</t>
+  </si>
+  <si>
+    <t>Pathfinder Second Edition</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/foundryvtt/pf2e/refs/heads/v14-dev/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>Scum and Villainy</t>
+  </si>
+  <si>
+    <t>https://github.com/drewg13/foundryvtt-scum-and-villainy</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/drewg13/foundryvtt-scum-and-villainy/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Starfinder Beginner Box Ruleset</t>
+  </si>
+  <si>
+    <t>https://github.com/ian612/sfrpgbb</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ian612/sfrpgbb/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Starfinder First Edition</t>
+  </si>
+  <si>
+    <t>https://github.com/foundryvtt-starfinder/foundryvtt-starfinder</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/foundryvtt-starfinder/foundryvtt-starfinder/refs/heads/development/static/lang/it.json</t>
+  </si>
+  <si>
+    <t>Starfinder Second Edition</t>
+  </si>
+  <si>
+    <t>sf2e</t>
+  </si>
+  <si>
+    <t>Shadowrun 6th Edition</t>
+  </si>
+  <si>
+    <t>https://github.com/yjeroen/foundry-shadowrun6-eden</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/yjeroen/foundry-shadowrun6-eden/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Slugblaster</t>
+  </si>
+  <si>
+    <t>https://github.com/MasterTomNL/slugblaster</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/MasterTomNL/slugblaster/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Star Trek Adventures 2d20 1E&amp;2E (Unofficial)</t>
+  </si>
+  <si>
+    <t>https://github.com/mkscho63/sta</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mkscho63/sta/refs/heads/main/lang/pt.json</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>Star Wars FFG system for Foundry VTT</t>
+  </si>
+  <si>
+    <t>https://github.com/StarWarsFoundryVTT/StarWarsFFG</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/StarWarsFoundryVTT/StarWarsFFG/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Savage Worlds Adventure Edition</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/peginc/swade/-/raw/develop/src/lang/en.yml?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/peginc/swade/</t>
+  </si>
+  <si>
+    <t>Ruins of Symbaroum 5E - Core System Module</t>
+  </si>
+  <si>
+    <t>https://github.com/FLPub/symbaroum5ecore</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/FLPub/symbaroum5ecore/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Twilight: 2000 (4th Edition)</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/twilight2000-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/twilight2000-foundry-vtt/refs/heads/master/src/lang/en.yml</t>
+  </si>
+  <si>
+    <t>Tales From the Loop</t>
+  </si>
+  <si>
+    <t>https://github.com/DrOgres/tftloop</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DrOgres/tftloop/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>The Witcher TRPG</t>
+  </si>
+  <si>
+    <t>https://github.com/witchertrpg-foundryvtt/TheWitcherTRPG</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/witchertrpg-foundryvtt/TheWitcherTRPG/refs/heads/main/lang/it.json</t>
+  </si>
+  <si>
+    <t>The One Ring 2nd Edition</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/herve.darritchon/foundryvtt-tor2e</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/herve.darritchon/foundryvtt-tor2e/-/raw/develop/src/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Twodsix - Cepheus &amp; Traveller (Unofficial)</t>
+  </si>
+  <si>
+    <t>https://github.com/xdy/twodsix-foundryvtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/xdy/twodsix-foundryvtt/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>Vaesen</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/vaesen-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/vaesen-foundry-vtt/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Warhammer: The Old World Roleplaying Game</t>
+  </si>
+  <si>
+    <t>https://github.com/moo-man/OldWorld-FoundryVTT</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/moo-man/OldWorld-FoundryVTT/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>The Wildsea (Unofficial)</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/pacosgrove1/wildsea-foundry</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/pacosgrove1/wildsea-foundry/-/raw/main/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Simple Worldbuilding System</t>
+  </si>
+  <si>
+    <t>https://github.com/foundryvtt/worldbuilding</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/foundryvtt/worldbuilding/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>World of Darkness 20th edition</t>
+  </si>
+  <si>
+    <t>https://github.com/JohanFalt/Foundry_WoD20</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/JohanFalt/Foundry_WoD20/refs/heads/main/lang/it.json</t>
+  </si>
+  <si>
+    <t>Coriolis: The Third Horizon</t>
+  </si>
+  <si>
+    <t>https://github.com/hodpub/yze-coriolis</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/hodpub/yze-coriolis/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>About Face</t>
+  </si>
+  <si>
+    <t>https://github.com/mclemente/about-face</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mclemente/about-face/refs/heads/master/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>About Time</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/about-time</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/about-time/-/raw/master/src/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Action Pack</t>
+  </si>
+  <si>
+    <t>https://github.com/teroparvinen/foundry-action-pack</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/teroparvinen/foundry-action-pack/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Active Auras</t>
+  </si>
+  <si>
+    <t>https://github.com/kandashi/Active-Auras</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/kandashi/Active-Auras/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Adventure Importer / Exporter</t>
+  </si>
+  <si>
+    <t>https://github.com/cstadther/adventure-import-export</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/cstadther/adventure-import-export/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Adventures in Middle-Earth</t>
+  </si>
+  <si>
+    <t>https://github.com/ZWinther/aime-module</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ZWinther/aime-module/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Always HP</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/always-hp</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/always-hp/blob/main/lang/it.json</t>
+  </si>
+  <si>
+    <t>Anonymous</t>
+  </si>
+  <si>
+    <t>https://github.com/reonZ/anonymous</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/reonZ/anonymous/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Arbron's Improved HP Bar</t>
+  </si>
+  <si>
+    <t>https://github.com/arbron/fvtt-hp-bar</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/arbron/fvtt-hp-bar/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Automated Animations</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/autoanimations/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/autoanimations</t>
+  </si>
+  <si>
+    <t>Babele</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/riccisi/foundryvtt-babele</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/riccisi/foundryvtt-babele/-/raw/master/module/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Better Rolltables</t>
+  </si>
+  <si>
+    <t>https://github.com/p4535992/foundryvtt-better-rolltables</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/p4535992/foundryvtt-better-rolltables/refs/heads/master/src/languages/en.json</t>
+  </si>
+  <si>
+    <t>Better Roofs</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Better-Roofs/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Better-Roofs/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>BG3 Inspired HUD - D&amp;D5e</t>
+  </si>
+  <si>
+    <t>https://github.com/BragginRites/bg3-hud-dnd5e</t>
+  </si>
+  <si>
+    <t>https://github.com/BragginRites/bg3-hud-dnd5e/blob/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Blades in the Dark Alternate Sheets</t>
+  </si>
+  <si>
+    <t>https://github.com/justinross/foundry-bitd-alternate-sheets</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/justinross/foundry-bitd-alternate-sheets/refs/heads/master/languages/it.json</t>
+  </si>
+  <si>
+    <t>Boss Bar</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Boss-Bar</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Boss-Bar/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Card Hands List</t>
+  </si>
+  <si>
+    <t>https://github.com/kristianserrano/card-hands-list</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/kristianserrano/card-hands-list/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Chat Portrait</t>
+  </si>
+  <si>
+    <t>https://github.com/p4535992/foundryvtt-chat-portrait</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/p4535992/foundryvtt-chat-portrait/refs/heads/master/src/languages/it.json</t>
+  </si>
+  <si>
+    <t>lib - ColorSettings</t>
+  </si>
+  <si>
+    <t>https://github.com/ardittristan/VTTColorSettings</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ardittristan/VTTColorSettings/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Combat Booster: Turn Marker, Recent Actions and more</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Combat-Booster</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Combat-Booster/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Combat Carousel</t>
+  </si>
+  <si>
+    <t>https://github.com/death-save/combat-carousel</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/death-save/combat-carousel/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Carousel Combat Tracker</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/combat-tracker-dock</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/combat-tracker-dock/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Combat Utility Belt</t>
+  </si>
+  <si>
+    <t>https://github.com/death-save/combat-utility-belt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/death-save/combat-utility-belt/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Compendium Browser</t>
+  </si>
+  <si>
+    <t>https://github.com/mclemente/compendium-browser</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mclemente/compendium-browser/refs/heads/master/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Compendium Folders</t>
+  </si>
+  <si>
+    <t>https://github.com/earlSt1/vtt-compendium-folders</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/earlSt1/vtt-compendium-folders/refs/heads/10x-update/lang/en.json</t>
+  </si>
+  <si>
+    <t>Complete Card Management</t>
+  </si>
+  <si>
+    <t>https://github.com/MetaMorphic-Digital/complete-card-management</t>
+  </si>
+  <si>
+    <t>https://github.com/MetaMorphic-Digital/complete-card-management/blob/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t>Modulo</t>
+  </si>
+  <si>
+    <t>Dynamic Active Effects</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/dae</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/dae/-/raw/v13/src/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Damage Log</t>
+  </si>
+  <si>
+    <t>https://codeberg.org/cs96and/FoundryVTT-damage-log</t>
+  </si>
+  <si>
+    <t>https://codeberg.org/cs96and/FoundryVTT-damage-log/raw/branch/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>DF Active Lights</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/tree/master/df-active-lights</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flamewave000/dragonflagon-fvtt/refs/heads/master/df-active-lights/lang/en.json</t>
+  </si>
+  <si>
+    <t>DF Curvy Walls</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/tree/master/df-curvy-walls</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flamewave000/dragonflagon-fvtt/refs/heads/master/df-curvy-walls/lang/en.json</t>
+  </si>
+  <si>
+    <t>DragonFlagon Quality of Life</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/tree/master/df-qol</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/blob/master/df-qol/lang/en.json</t>
+  </si>
+  <si>
+    <t>DFreds Convenient Effects</t>
+  </si>
+  <si>
+    <t>https://github.com/DFreds/dfreds-convenient-effects</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/DFreds/dfreds-convenient-effects/refs/heads/main/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>DF Scene Enhancement</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/tree/master/df-scene-enhance</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flamewave000/dragonflagon-fvtt/refs/heads/master/df-scene-enhance/lang/en.json</t>
+  </si>
+  <si>
+    <t>DF Settings Clarity</t>
+  </si>
+  <si>
+    <t>https://github.com/flamewave000/dragonflagon-fvtt/tree/master/df-settings-clarity</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/flamewave000/dragonflagon-fvtt/refs/heads/master/df-settings-clarity/lang/en.json</t>
+  </si>
+  <si>
+    <t>Dice Tray</t>
+  </si>
+  <si>
+    <t>https://github.com/mclemente/fvtt-dice-tray</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mclemente/fvtt-dice-tray/refs/heads/master/src/lang/it.json</t>
+  </si>
+  <si>
+    <t>Dice So Nice!</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/riccisi/foundryvtt-dice-so-nice</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/riccisi/foundryvtt-dice-so-nice/-/raw/master/module/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Dragonbane - Item Browser</t>
+  </si>
+  <si>
+    <t>https://github.com/bb46003/Dragonbane---Item-Browser/tree/main</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/bb46003/Dragonbane---Item-Browser/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Drag Ruler</t>
+  </si>
+  <si>
+    <t>https://github.com/manuelVo/foundryvtt-drag-ruler/tree/master</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/manuelVo/foundryvtt-drag-ruler/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Dungeon Draw</t>
+  </si>
+  <si>
+    <t>https://github.com/mcglincy/dungeondraw-foundry-vtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mcglincy/dungeondraw-foundry-vtt/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Easy Target</t>
+  </si>
+  <si>
+    <t>https://bitbucket.org/Fyorl/easy-target/src/master/</t>
+  </si>
+  <si>
+    <t>https://bitbucket.org/Fyorl/easy-target/raw/b08eba468d614f6ee2da553e49105dc6414b11c8/lang/en.json</t>
+  </si>
+  <si>
+    <t>Argon - Combat HUD (CORE)</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/enhancedcombathud</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/enhancedcombathud/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Argon - Combat HUD (DND5E)</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/enhancedcombathud-dnd5e</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/enhancedcombathud-dnd5e/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Argon - Combat HUD (DRAGONBANE)</t>
+  </si>
+  <si>
+    <t>https://github.com/rayners/enhancedcombathud-dragonbane</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/rayners/enhancedcombathud-dragonbane/refs/heads/main/src/languages/en.json</t>
+  </si>
+  <si>
+    <t>Enhanced Terrain Layer</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/enhanced-terrain-layer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/enhanced-terrain-layer/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Foundry Achievements</t>
+  </si>
+  <si>
+    <t>https://github.com/Handyfon/Farchievements</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Handyfon/Farchievements/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Fog Manager</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tiwato/fogmanager</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tiwato/fogmanager/-/raw/master/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Forien's Copy Environment</t>
+  </si>
+  <si>
+    <t>https://github.com/League-of-Foundry-Developers/foundryvtt-forien-copy-environment</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/League-of-Foundry-Developers/foundryvtt-forien-copy-environment/refs/heads/master/languages/it.json</t>
+  </si>
+  <si>
+    <t>Forien's Quest Log</t>
+  </si>
+  <si>
+    <t>https://github.com/Forien/foundryvtt-forien-quest-log</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Forien/foundryvtt-forien-quest-log/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Forien's Scene Navigator</t>
+  </si>
+  <si>
+    <t>https://github.com/Forien/foundryvtt-forien-scene-navigator</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Forien/foundryvtt-forien-scene-navigator/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Party Resources</t>
+  </si>
+  <si>
+    <t>https://github.com/davelens/fvtt-party-resources</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/davelens/fvtt-party-resources/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Gambit's FXMaster</t>
+  </si>
+  <si>
+    <t>https://github.com/gambit07/fxmaster</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/gambit07/fxmaster/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Card Hand Mini Toolba</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/pengrath/hand-mini-bar</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/pengrath/hand-mini-bar/-/raw/main/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Health Estimate</t>
+  </si>
+  <si>
+    <t>https://github.com/mclemente/healthEstimate/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mclemente/healthEstimate/refs/heads/master/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Health Monitor</t>
+  </si>
+  <si>
+    <t>https://github.com/jessev14/health-monitor</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jessev14/health-monitor/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Hot Pan &amp; Zoom!</t>
+  </si>
+  <si>
+    <t>https://github.com/coffiarts/FoundryVTT-hot-pan</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/coffiarts/FoundryVTT-hot-pan/refs/heads/master/src/hot-pan/lang/en.json</t>
+  </si>
+  <si>
+    <t>Illandril's Hotbar Uses</t>
+  </si>
+  <si>
+    <t>https://github.com/illandril/FoundryVTT-hotbar-uses</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/illandril/FoundryVTT-hotbar-uses/refs/heads/main/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Innocenti's Loot</t>
+  </si>
+  <si>
+    <t>https://github.com/rinnocenti/innocenti-loot</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/rinnocenti/innocenti-loot/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Innocenti Open Lock</t>
+  </si>
+  <si>
+    <t>https://github.com/rinnocenti/innocenti-openlock</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/rinnocenti/innocenti-openlock/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Item Macro</t>
+  </si>
+  <si>
+    <t>https://github.com/Foundry-Workshop/Item-Macro</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Foundry-Workshop/Item-Macro/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Item Collection</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/itemcollection</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/itemcollection/-/raw/dndv3/src/lang/it.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Lancer Initiative</t>
+  </si>
+  <si>
+    <t>https://codeberg.org/Bolts/lancer-initiative</t>
+  </si>
+  <si>
+    <t>https://codeberg.org/Bolts/lancer-initiative/raw/branch/main/public/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Levels</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Levels/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Let Me Roll That For You</t>
+  </si>
+  <si>
+    <t>Levels</t>
+  </si>
+  <si>
+    <t>https://github.com/League-of-Foundry-Developers/fvtt-module-lmrtfy</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/League-of-Foundry-Developers/fvtt-module-lmrtfy/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Lord of the Rings Roleplaying</t>
+  </si>
+  <si>
+    <t>https://github.com/ZWinther/lotr5e-module</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ZWinther/lotr5e-module/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Masks: A New Generation</t>
+  </si>
+  <si>
+    <t>https://github.com/philote/masks-newgeneration-unofficial</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/philote/masks-newgeneration-unofficial/refs/heads/main/languages/en.json</t>
+  </si>
+  <si>
+    <t>Merchant Sheet NPC</t>
+  </si>
+  <si>
+    <t>https://github.com/whelan/fvtt-merchant-sheet-npc</t>
+  </si>
+  <si>
+    <t>Monarch</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/whelan/fvtt-merchant-sheet-npc/refs/heads/main/Source/lang/en.json</t>
+  </si>
+  <si>
+    <t>Metric System for D&amp;D5e</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundry-vtt/foundryvtt-metricsystem-module</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundry-vtt/foundryvtt-metricsystem-module/-/raw/master/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Midi Quality of Life Improvements</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/midi-qol</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/midi-qol/-/raw/v13/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Minimal U</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/saif-ellafi/foundryvtt-minimal-ui/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>https://github.com/saif-ellafi/foundryvtt-minimal-ui</t>
+  </si>
+  <si>
+    <t>https://github.com/zeel01/monarch</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/zeel01/monarch/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Active Tile Triggers</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-active-tiles/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-active-tiles/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Bloodsplats</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-bloodsplats</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-bloodsplats/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Combat Details</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-combat-details</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-combat-details/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Patrol</t>
+  </si>
+  <si>
+    <t>Pings</t>
+  </si>
+  <si>
+    <t>Monk's Combat Marker</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-combat-marker</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-combat-marker/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Hotbar Expansion</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/hotbar-expansion</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/hotbar-expansion/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Scene Navigation</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-scene-navigation</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-scene-navigation/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's TokenBar</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-tokenbar</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-tokenbar/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Monk's Wall Enhancement</t>
+  </si>
+  <si>
+    <t>https://github.com/ironmonk108/monks-wall-enhancement</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/ironmonk108/monks-wall-enhancement/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Alien RPG - Motion Tracker</t>
+  </si>
+  <si>
+    <t>https://github.com/pplans/foundry-vtt-module-motion-tracker</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/pplans/foundry-vtt-module-motion-tracker/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Multilevel Tokens</t>
+  </si>
+  <si>
+    <t>https://github.com/BeneosBattlemaps/Beneos-Multilevel-Tokens</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/BeneosBattlemaps/Beneos-Multilevel-Tokens/refs/heads/main/lang/it.json</t>
+  </si>
+  <si>
+    <t>Baileywiki Mass Edit</t>
+  </si>
+  <si>
+    <t>https://github.com/Aedif/multi-token-edit</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Aedif/multi-token-edit/refs/heads/main/multi-token-edit/lang/en.json</t>
+  </si>
+  <si>
+    <t>poi-teleport</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Patrol</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Patrol/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Perfect Vision</t>
+  </si>
+  <si>
+    <t>https://github.com/dev7355608/perfect-vision</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/dev7355608/perfect-vision/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Pin Cushion</t>
+  </si>
+  <si>
+    <t>https://github.com/p4535992/foundryvtt-pin-cushion/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/p4535992/foundryvtt-pin-cushion/refs/heads/master/src/languages/en.json</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundry-azzurite/pings/</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/foundry-azzurite/pings/-/raw/master/resources/languages/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Point of Interest Teleporter</t>
+  </si>
+  <si>
+    <t>https://github.com/BeneosBattlemaps/Beneos-Point-Of-Interest-Teleporter</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/BeneosBattlemaps/Beneos-Point-Of-Interest-Teleporter/refs/heads/main/lang/it.json</t>
+  </si>
+  <si>
+    <t>PnP - Pointer and Pings</t>
+  </si>
+  <si>
+    <t>https://github.com/p4535992/foundryvtt-pointer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/p4535992/foundryvtt-pointer/refs/heads/master/src/languages/en.json</t>
+  </si>
+  <si>
+    <t>Polyglot</t>
+  </si>
+  <si>
+    <t>https://github.com/mclemente/fvtt-module-polyglot</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mclemente/fvtt-module-polyglot/refs/heads/master/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>PopOut!</t>
+  </si>
+  <si>
+    <t>https://github.com/League-of-Foundry-Developers/fvtt-module-popout</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/League-of-Foundry-Developers/fvtt-module-popout/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/portal-lib</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/portal-lib/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Quick Insert - Search Widget</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/fvtt-modules-lab/quick-insert</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/fvtt-modules-lab/quick-insert/-/raw/master/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Raise My Hand</t>
+  </si>
+  <si>
+    <t>https://github.com/henry-malinowski/raise-my-hand-plus</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/henry-malinowski/raise-my-hand-plus/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Rarity Colors</t>
+  </si>
+  <si>
+    <t>https://github.com/p4535992/foundryvtt-rarity-colors</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/p4535992/foundryvtt-rarity-colors/refs/heads/master/src/languages/en.json</t>
+  </si>
+  <si>
+    <t>Ready Set Roll for D&amp;D5e</t>
+  </si>
+  <si>
+    <t>https://github.com/MangoFVTT/fvtt-ready-set-roll-5e</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/MangoFVTT/fvtt-ready-set-roll-5e/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Rideable</t>
+  </si>
+  <si>
+    <t>https://github.com/Saibot393/Rideable</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Saibot393/Rideable/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Sequencer</t>
+  </si>
+  <si>
+    <t>https://github.com/fantasycalendar/FoundryVTT-Sequencer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fantasycalendar/FoundryVTT-Sequencer/refs/heads/master/languages/en-EN.json</t>
+  </si>
+  <si>
+    <t>Shared Vision</t>
+  </si>
+  <si>
+    <t>https://github.com/MaterialFoundry/SharedVision</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/MaterialFoundry/SharedVision/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Simple Calendar</t>
+  </si>
+  <si>
+    <t>https://github.com/vigoren/foundryvtt-simple-calendar</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/vigoren/foundryvtt-simple-calendar/refs/heads/main/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Simple Dice Roller</t>
+  </si>
+  <si>
+    <t>https://github.com/jopeek/fvtt-simple-dice-roller/</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/jopeek/fvtt-simple-dice-roller/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Simple Weather</t>
+  </si>
+  <si>
+    <t>https://github.com/dovrosenberg/foundry-simple-weather</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/dovrosenberg/foundry-simple-weather/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>Smart Target</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Smart-Target</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Smart-Target/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Splatter</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Splatter</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Splatter/refs/heads/main/languages/en.json</t>
+  </si>
+  <si>
+    <t>Storyteller</t>
+  </si>
+  <si>
+    <t>https://github.com/Xbozon/storyteller</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Xbozon/storyteller/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Swade Tools</t>
+  </si>
+  <si>
+    <t>https://github.com/lipefl/swade-tools</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/lipefl/swade-tools/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Terrain Height Tools</t>
+  </si>
+  <si>
+    <t>https://github.com/Wibble199/FoundryVTT-Terrain-Height-Tools</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Wibble199/FoundryVTT-Terrain-Height-Tools/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Terrain Ruler</t>
+  </si>
+  <si>
+    <t>https://github.com/manuelVo/foundryvtt-terrain-ruler/tree/master</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/manuelVo/foundryvtt-terrain-ruler/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Tidy 5e Sheets</t>
+  </si>
+  <si>
+    <t>https://github.com/kgar/foundry-vtt-tidy-5e-sheets</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/kgar/foundry-vtt-tidy-5e-sheets/refs/heads/main/public/lang/en.json</t>
+  </si>
+  <si>
+    <t>Tidy UI Game Settings</t>
+  </si>
+  <si>
+    <t>https://github.com/sdenec/tidy-ui_game-settings</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/sdenec/tidy-ui_game-settings/refs/heads/master/src/langs/en.json</t>
+  </si>
+  <si>
+    <t>Tile Scroll</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/tile-scroll</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/tile-scroll/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Times Up</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/times-up</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/tposney/times-up/-/raw/master/src/lang/en.json?ref_type=heads&amp;inline=false</t>
+  </si>
+  <si>
+    <t>Token Action HUD Core</t>
+  </si>
+  <si>
+    <t>https://github.com/Larkinabout/fvtt-token-action-hud-core</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Larkinabout/fvtt-token-action-hud-core/refs/heads/main/languages/it.json</t>
+  </si>
+  <si>
+    <t>Token Action HUD D&amp;D 5e</t>
+  </si>
+  <si>
+    <t>https://github.com/Larkinabout/fvtt-token-action-hud-dnd5e</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Larkinabout/fvtt-token-action-hud-dnd5e/refs/heads/main/languages/it.json</t>
+  </si>
+  <si>
+    <t>Token Attacher</t>
+  </si>
+  <si>
+    <t>https://github.com/KayelGee/token-attacher</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/KayelGee/token-attacher/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Token Auras</t>
+  </si>
+  <si>
+    <t>https://bitbucket.org/Fyorl/token-auras/src/master/</t>
+  </si>
+  <si>
+    <t>https://bitbucket.org/Fyorl/token-auras/raw/c7c0aa5db2dbbb45582c933a9a458cea09ee9c5e/lang/it.json</t>
+  </si>
+  <si>
+    <t>Token HUD Wildcard</t>
+  </si>
+  <si>
+    <t>https://github.com/mhilbrunner/token-hud-wildcard</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/mhilbrunner/token-hud-wildcard/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Token Magic FX</t>
+  </si>
+  <si>
+    <t>https://github.com/Feu-Secret/Tokenmagic</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Feu-Secret/Tokenmagic/refs/heads/master/tokenmagic/lang/en.json</t>
+  </si>
+  <si>
+    <t>Token Mold</t>
+  </si>
+  <si>
+    <t>https://github.com/Moerill/token-mold#token-mold</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Moerill/token-mold/refs/heads/master/lang/en.json</t>
+  </si>
+  <si>
+    <t>Turn Marker</t>
+  </si>
+  <si>
+    <t>https://github.com/kckaiwei/TurnMarker-alt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/kckaiwei/TurnMarker-alt/refs/heads/main/src/lang/en.json</t>
+  </si>
+  <si>
+    <t>Vision 5e</t>
+  </si>
+  <si>
+    <t>https://github.com/dev7355608/vision-5e</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/dev7355608/vision-5e/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Tokenizer: The Token Editor</t>
+  </si>
+  <si>
+    <t>https://github.com/MrPrimate/tokenizer</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/MrPrimate/tokenizer/refs/heads/master/lang/it.json</t>
+  </si>
+  <si>
+    <t>Wall Height</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/wall-height</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/wall-height/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Warhammer Library</t>
+  </si>
+  <si>
+    <t>https://github.com/moo-man/WarhammerLibrary-FVTT</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/moo-man/WarhammerLibrary-FVTT/refs/heads/master/static/lang/en.json</t>
+  </si>
+  <si>
+    <t>Weather Blocker</t>
+  </si>
+  <si>
+    <t>https://github.com/theripper93/Weather-Blocker</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/theripper93/Weather-Blocker/refs/heads/main/lang/en.json</t>
+  </si>
+  <si>
+    <t>Weather FX</t>
+  </si>
+  <si>
+    <t>https://github.com/LeafWulf/weatherfx</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/LeafWulf/weatherfx/refs/heads/master/languages/en.json</t>
+  </si>
+  <si>
+    <t>Year Zero Engine: Combat</t>
+  </si>
+  <si>
+    <t>https://github.com/fvtt-fria-ligan/yearzero-combat-fvtt</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/fvtt-fria-ligan/yearzero-combat-fvtt/refs/heads/main/src/lang/en.yml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -665,13 +2317,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1004,1005 +2659,3766 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB846EEA-B0CC-4DA6-843C-1EE5583E7F70}">
-  <dimension ref="A1:A201"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="63.5703125" customWidth="1"/>
+    <col min="4" max="4" width="114.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E12" t="s">
+        <v>276</v>
+      </c>
+      <c r="F12" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" t="s">
+        <v>275</v>
+      </c>
+      <c r="F13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>275</v>
+      </c>
+      <c r="F15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" t="s">
+        <v>275</v>
+      </c>
+      <c r="F16" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" t="s">
+        <v>233</v>
+      </c>
+      <c r="E18" t="s">
+        <v>275</v>
+      </c>
+      <c r="F18" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19" t="s">
+        <v>276</v>
+      </c>
+      <c r="F19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" t="s">
+        <v>245</v>
+      </c>
+      <c r="E21" t="s">
+        <v>275</v>
+      </c>
+      <c r="F21" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>250</v>
+      </c>
+      <c r="C23" t="s">
+        <v>251</v>
+      </c>
+      <c r="D23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E23" t="s">
+        <v>275</v>
+      </c>
+      <c r="F23" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E24" t="s">
+        <v>275</v>
+      </c>
+      <c r="F24" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" t="s">
+        <v>275</v>
+      </c>
+      <c r="F25" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B26" t="s">
+        <v>259</v>
+      </c>
+      <c r="C26" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E26" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" t="s">
+        <v>264</v>
+      </c>
+      <c r="E27" t="s">
+        <v>275</v>
+      </c>
+      <c r="F27" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" t="s">
+        <v>275</v>
+      </c>
+      <c r="F28" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" t="s">
+        <v>269</v>
+      </c>
+      <c r="D29" t="s">
+        <v>270</v>
+      </c>
+      <c r="E29" t="s">
+        <v>275</v>
+      </c>
+      <c r="F29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" t="s">
+        <v>273</v>
+      </c>
+      <c r="E30" t="s">
+        <v>276</v>
+      </c>
+      <c r="F30" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C31" t="s">
+        <v>278</v>
+      </c>
+      <c r="D31" t="s">
+        <v>279</v>
+      </c>
+      <c r="E31" t="s">
+        <v>275</v>
+      </c>
+      <c r="F31" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B33" t="s">
+        <v>282</v>
+      </c>
+      <c r="C33" t="s">
+        <v>283</v>
+      </c>
+      <c r="D33" t="s">
+        <v>284</v>
+      </c>
+      <c r="E33" t="s">
+        <v>275</v>
+      </c>
+      <c r="F33" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B34" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D34" t="s">
+        <v>286</v>
+      </c>
+      <c r="E34" t="s">
+        <v>275</v>
+      </c>
+      <c r="F34" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B35" t="s">
+        <v>287</v>
+      </c>
+      <c r="C35" t="s">
+        <v>288</v>
+      </c>
+      <c r="D35" t="s">
+        <v>289</v>
+      </c>
+      <c r="E35" t="s">
+        <v>275</v>
+      </c>
+      <c r="F35" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B36" t="s">
+        <v>290</v>
+      </c>
+      <c r="C36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D36" t="s">
+        <v>292</v>
+      </c>
+      <c r="E36" t="s">
+        <v>276</v>
+      </c>
+      <c r="F36" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" t="s">
+        <v>296</v>
+      </c>
+      <c r="F37" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B38" t="s">
+        <v>297</v>
+      </c>
+      <c r="C38" t="s">
+        <v>298</v>
+      </c>
+      <c r="D38" t="s">
+        <v>299</v>
+      </c>
+      <c r="E38" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>300</v>
+      </c>
+      <c r="B39" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" t="s">
+        <v>301</v>
+      </c>
+      <c r="D39" t="s">
+        <v>303</v>
+      </c>
+      <c r="E39" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C40" t="s">
+        <v>305</v>
+      </c>
+      <c r="D40" t="s">
+        <v>306</v>
+      </c>
+      <c r="E40" t="s">
+        <v>275</v>
+      </c>
+      <c r="F40" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
+        <v>310</v>
+      </c>
+      <c r="C41" t="s">
+        <v>311</v>
+      </c>
+      <c r="D41" t="s">
+        <v>312</v>
+      </c>
+      <c r="E41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F41" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>314</v>
+      </c>
+      <c r="B42" t="s">
+        <v>313</v>
+      </c>
+      <c r="C42" t="s">
+        <v>301</v>
+      </c>
+      <c r="D42" t="s">
+        <v>303</v>
+      </c>
+      <c r="E42" t="s">
+        <v>275</v>
+      </c>
+      <c r="F42" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B43" t="s">
+        <v>307</v>
+      </c>
+      <c r="C43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D43" t="s">
+        <v>309</v>
+      </c>
+      <c r="E43" t="s">
+        <v>275</v>
+      </c>
+      <c r="F43" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B44" t="s">
+        <v>315</v>
+      </c>
+      <c r="C44" t="s">
+        <v>316</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E44" t="s">
+        <v>275</v>
+      </c>
+      <c r="F44" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B45" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" t="s">
+        <v>319</v>
+      </c>
+      <c r="D45" t="s">
+        <v>320</v>
+      </c>
+      <c r="E45" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B46" t="s">
+        <v>321</v>
+      </c>
+      <c r="C46" t="s">
+        <v>322</v>
+      </c>
+      <c r="D46" t="s">
+        <v>323</v>
+      </c>
+      <c r="E46" t="s">
+        <v>324</v>
+      </c>
+      <c r="F46" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="B47" t="s">
+        <v>325</v>
+      </c>
+      <c r="C47" t="s">
+        <v>326</v>
+      </c>
+      <c r="D47" t="s">
+        <v>327</v>
+      </c>
+      <c r="E47" t="s">
+        <v>275</v>
+      </c>
+      <c r="F47" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="B48" t="s">
+        <v>328</v>
+      </c>
+      <c r="C48" t="s">
+        <v>330</v>
+      </c>
+      <c r="D48" t="s">
+        <v>329</v>
+      </c>
+      <c r="E48" t="s">
+        <v>275</v>
+      </c>
+      <c r="F48" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="B49" t="s">
+        <v>331</v>
+      </c>
+      <c r="C49" t="s">
+        <v>332</v>
+      </c>
+      <c r="D49" t="s">
+        <v>333</v>
+      </c>
+      <c r="E49" t="s">
+        <v>275</v>
+      </c>
+      <c r="F49" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B50" t="s">
+        <v>334</v>
+      </c>
+      <c r="C50" t="s">
+        <v>335</v>
+      </c>
+      <c r="D50" t="s">
+        <v>336</v>
+      </c>
+      <c r="E50" t="s">
+        <v>275</v>
+      </c>
+      <c r="F50" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="B51" t="s">
+        <v>337</v>
+      </c>
+      <c r="C51" t="s">
+        <v>338</v>
+      </c>
+      <c r="D51" t="s">
+        <v>339</v>
+      </c>
+      <c r="E51" t="s">
+        <v>275</v>
+      </c>
+      <c r="F51" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B52" t="s">
+        <v>340</v>
+      </c>
+      <c r="C52" t="s">
+        <v>341</v>
+      </c>
+      <c r="D52" t="s">
+        <v>342</v>
+      </c>
+      <c r="E52" t="s">
+        <v>276</v>
+      </c>
+      <c r="F52" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B53" t="s">
+        <v>343</v>
+      </c>
+      <c r="C53" t="s">
+        <v>344</v>
+      </c>
+      <c r="D53" t="s">
+        <v>345</v>
+      </c>
+      <c r="E53" t="s">
+        <v>276</v>
+      </c>
+      <c r="F53" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B54" t="s">
+        <v>346</v>
+      </c>
+      <c r="C54" t="s">
+        <v>347</v>
+      </c>
+      <c r="D54" t="s">
+        <v>348</v>
+      </c>
+      <c r="E54" t="s">
+        <v>275</v>
+      </c>
+      <c r="F54" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C55" t="s">
+        <v>350</v>
+      </c>
+      <c r="D55" t="s">
+        <v>351</v>
+      </c>
+      <c r="E55" t="s">
+        <v>275</v>
+      </c>
+      <c r="F55" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B56" t="s">
+        <v>352</v>
+      </c>
+      <c r="C56" t="s">
+        <v>353</v>
+      </c>
+      <c r="D56" t="s">
+        <v>354</v>
+      </c>
+      <c r="E56" t="s">
+        <v>275</v>
+      </c>
+      <c r="F56" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B57" t="s">
+        <v>355</v>
+      </c>
+      <c r="C57" t="s">
+        <v>356</v>
+      </c>
+      <c r="D57" t="s">
+        <v>357</v>
+      </c>
+      <c r="E57" t="s">
+        <v>275</v>
+      </c>
+      <c r="F57" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B58" t="s">
+        <v>358</v>
+      </c>
+      <c r="C58" t="s">
+        <v>359</v>
+      </c>
+      <c r="D58" t="s">
+        <v>360</v>
+      </c>
+      <c r="E58" t="s">
+        <v>275</v>
+      </c>
+      <c r="F58" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+      <c r="B59" t="s">
+        <v>361</v>
+      </c>
+      <c r="C59" t="s">
+        <v>362</v>
+      </c>
+      <c r="D59" t="s">
+        <v>363</v>
+      </c>
+      <c r="E59" t="s">
+        <v>276</v>
+      </c>
+      <c r="F59" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B60" t="s">
+        <v>364</v>
+      </c>
+      <c r="C60" t="s">
+        <v>365</v>
+      </c>
+      <c r="D60" t="s">
+        <v>366</v>
+      </c>
+      <c r="E60" t="s">
+        <v>275</v>
+      </c>
+      <c r="F60" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B62" t="s">
+        <v>367</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D62" t="s">
+        <v>369</v>
+      </c>
+      <c r="E62" t="s">
+        <v>275</v>
+      </c>
+      <c r="F62" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="B63" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" t="s">
+        <v>371</v>
+      </c>
+      <c r="D63" t="s">
+        <v>372</v>
+      </c>
+      <c r="E63" t="s">
+        <v>276</v>
+      </c>
+      <c r="F63" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="B64" t="s">
+        <v>373</v>
+      </c>
+      <c r="C64" t="s">
+        <v>374</v>
+      </c>
+      <c r="D64" t="s">
+        <v>375</v>
+      </c>
+      <c r="E64" t="s">
+        <v>275</v>
+      </c>
+      <c r="F64" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="B65" t="s">
+        <v>376</v>
+      </c>
+      <c r="C65" t="s">
+        <v>377</v>
+      </c>
+      <c r="D65" t="s">
+        <v>378</v>
+      </c>
+      <c r="E65" t="s">
+        <v>275</v>
+      </c>
+      <c r="F65" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B66" t="s">
+        <v>379</v>
+      </c>
+      <c r="C66" t="s">
+        <v>380</v>
+      </c>
+      <c r="D66" t="s">
+        <v>381</v>
+      </c>
+      <c r="E66" t="s">
+        <v>275</v>
+      </c>
+      <c r="F66" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B67" t="s">
+        <v>382</v>
+      </c>
+      <c r="C67" t="s">
+        <v>383</v>
+      </c>
+      <c r="D67" t="s">
+        <v>384</v>
+      </c>
+      <c r="E67" t="s">
+        <v>275</v>
+      </c>
+      <c r="F67" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="B68" t="s">
+        <v>385</v>
+      </c>
+      <c r="C68" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" t="s">
+        <v>387</v>
+      </c>
+      <c r="E68" t="s">
+        <v>276</v>
+      </c>
+      <c r="F68" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="B69" t="s">
+        <v>388</v>
+      </c>
+      <c r="C69" t="s">
+        <v>389</v>
+      </c>
+      <c r="D69" t="s">
+        <v>390</v>
+      </c>
+      <c r="E69" t="s">
+        <v>275</v>
+      </c>
+      <c r="F69" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B70" t="s">
+        <v>391</v>
+      </c>
+      <c r="C70" t="s">
+        <v>392</v>
+      </c>
+      <c r="D70" t="s">
+        <v>393</v>
+      </c>
+      <c r="E70" t="s">
+        <v>275</v>
+      </c>
+      <c r="F70" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B71" t="s">
+        <v>394</v>
+      </c>
+      <c r="C71" t="s">
+        <v>396</v>
+      </c>
+      <c r="D71" t="s">
+        <v>395</v>
+      </c>
+      <c r="E71" t="s">
+        <v>275</v>
+      </c>
+      <c r="F71" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="B72" t="s">
+        <v>397</v>
+      </c>
+      <c r="C72" t="s">
+        <v>398</v>
+      </c>
+      <c r="D72" t="s">
+        <v>399</v>
+      </c>
+      <c r="E72" t="s">
+        <v>276</v>
+      </c>
+      <c r="F72" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B73" t="s">
+        <v>400</v>
+      </c>
+      <c r="C73" t="s">
+        <v>401</v>
+      </c>
+      <c r="D73" t="s">
+        <v>402</v>
+      </c>
+      <c r="E73" t="s">
+        <v>275</v>
+      </c>
+      <c r="F73" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B74" t="s">
+        <v>403</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D74" t="s">
+        <v>405</v>
+      </c>
+      <c r="E74" t="s">
+        <v>275</v>
+      </c>
+      <c r="F74" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B75" t="s">
+        <v>406</v>
+      </c>
+      <c r="C75" t="s">
+        <v>407</v>
+      </c>
+      <c r="D75" t="s">
+        <v>408</v>
+      </c>
+      <c r="E75" t="s">
+        <v>275</v>
+      </c>
+      <c r="F75" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B76" t="s">
+        <v>409</v>
+      </c>
+      <c r="C76" t="s">
+        <v>410</v>
+      </c>
+      <c r="D76" t="s">
+        <v>411</v>
+      </c>
+      <c r="E76" t="s">
+        <v>276</v>
+      </c>
+      <c r="F76" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
+        <v>412</v>
+      </c>
+      <c r="C77" t="s">
+        <v>413</v>
+      </c>
+      <c r="D77" t="s">
+        <v>414</v>
+      </c>
+      <c r="E77" t="s">
+        <v>275</v>
+      </c>
+      <c r="F77" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B78" t="s">
+        <v>415</v>
+      </c>
+      <c r="C78" t="s">
+        <v>416</v>
+      </c>
+      <c r="D78" t="s">
+        <v>417</v>
+      </c>
+      <c r="E78" t="s">
+        <v>275</v>
+      </c>
+      <c r="F78" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B79" t="s">
+        <v>418</v>
+      </c>
+      <c r="C79" t="s">
+        <v>419</v>
+      </c>
+      <c r="D79" t="s">
+        <v>420</v>
+      </c>
+      <c r="E79" t="s">
+        <v>276</v>
+      </c>
+      <c r="F79" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B80" t="s">
+        <v>421</v>
+      </c>
+      <c r="C80" t="s">
+        <v>422</v>
+      </c>
+      <c r="D80" t="s">
+        <v>423</v>
+      </c>
+      <c r="E80" t="s">
+        <v>275</v>
+      </c>
+      <c r="F80" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="B81" t="s">
+        <v>424</v>
+      </c>
+      <c r="C81" t="s">
+        <v>425</v>
+      </c>
+      <c r="D81" t="s">
+        <v>426</v>
+      </c>
+      <c r="E81" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B82" t="s">
+        <v>427</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D82" t="s">
+        <v>429</v>
+      </c>
+      <c r="E82" t="s">
+        <v>275</v>
+      </c>
+      <c r="F82" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B83" t="s">
+        <v>430</v>
+      </c>
+      <c r="C83" t="s">
+        <v>431</v>
+      </c>
+      <c r="D83" t="s">
+        <v>432</v>
+      </c>
+      <c r="E83" t="s">
+        <v>275</v>
+      </c>
+      <c r="F83" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B84" t="s">
+        <v>433</v>
+      </c>
+      <c r="C84" t="s">
+        <v>434</v>
+      </c>
+      <c r="D84" t="s">
+        <v>435</v>
+      </c>
+      <c r="E84" t="s">
+        <v>275</v>
+      </c>
+      <c r="F84" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B85" t="s">
+        <v>436</v>
+      </c>
+      <c r="C85" t="s">
+        <v>437</v>
+      </c>
+      <c r="D85" t="s">
+        <v>438</v>
+      </c>
+      <c r="E85" t="s">
+        <v>275</v>
+      </c>
+      <c r="F85" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="B86" t="s">
+        <v>439</v>
+      </c>
+      <c r="C86" t="s">
+        <v>440</v>
+      </c>
+      <c r="D86" t="s">
+        <v>441</v>
+      </c>
+      <c r="E86" t="s">
+        <v>275</v>
+      </c>
+      <c r="F86" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B87" t="s">
+        <v>442</v>
+      </c>
+      <c r="C87" t="s">
+        <v>443</v>
+      </c>
+      <c r="D87" t="s">
+        <v>444</v>
+      </c>
+      <c r="E87" t="s">
+        <v>275</v>
+      </c>
+      <c r="F87" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B88" t="s">
+        <v>448</v>
+      </c>
+      <c r="C88" t="s">
+        <v>449</v>
+      </c>
+      <c r="D88" t="s">
+        <v>450</v>
+      </c>
+      <c r="E88" t="s">
+        <v>275</v>
+      </c>
+      <c r="F88" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B89" t="s">
+        <v>451</v>
+      </c>
+      <c r="C89" t="s">
+        <v>452</v>
+      </c>
+      <c r="D89" t="s">
+        <v>453</v>
+      </c>
+      <c r="E89" t="s">
+        <v>275</v>
+      </c>
+      <c r="F89" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B90" t="s">
+        <v>454</v>
+      </c>
+      <c r="C90" t="s">
+        <v>455</v>
+      </c>
+      <c r="D90" t="s">
+        <v>456</v>
+      </c>
+      <c r="E90" t="s">
+        <v>275</v>
+      </c>
+      <c r="F90" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B91" t="s">
+        <v>457</v>
+      </c>
+      <c r="C91" t="s">
+        <v>458</v>
+      </c>
+      <c r="D91" t="s">
+        <v>459</v>
+      </c>
+      <c r="E91" t="s">
+        <v>275</v>
+      </c>
+      <c r="F91" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B92" t="s">
+        <v>460</v>
+      </c>
+      <c r="C92" t="s">
+        <v>461</v>
+      </c>
+      <c r="D92" t="s">
+        <v>462</v>
+      </c>
+      <c r="E92" t="s">
+        <v>275</v>
+      </c>
+      <c r="F92" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B93" t="s">
+        <v>463</v>
+      </c>
+      <c r="C93" t="s">
+        <v>464</v>
+      </c>
+      <c r="D93" t="s">
+        <v>465</v>
+      </c>
+      <c r="E93" t="s">
+        <v>275</v>
+      </c>
+      <c r="F93" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B94" t="s">
+        <v>466</v>
+      </c>
+      <c r="C94" t="s">
+        <v>467</v>
+      </c>
+      <c r="D94" t="s">
+        <v>468</v>
+      </c>
+      <c r="E94" t="s">
+        <v>275</v>
+      </c>
+      <c r="F94" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B95" t="s">
+        <v>469</v>
+      </c>
+      <c r="C95" t="s">
+        <v>470</v>
+      </c>
+      <c r="D95" t="s">
+        <v>471</v>
+      </c>
+      <c r="E95" t="s">
+        <v>275</v>
+      </c>
+      <c r="F95" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="B96" t="s">
+        <v>472</v>
+      </c>
+      <c r="C96" t="s">
+        <v>473</v>
+      </c>
+      <c r="D96" t="s">
+        <v>474</v>
+      </c>
+      <c r="E96" t="s">
+        <v>276</v>
+      </c>
+      <c r="F96" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="B97" t="s">
+        <v>475</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D97" t="s">
+        <v>477</v>
+      </c>
+      <c r="E97" t="s">
+        <v>275</v>
+      </c>
+      <c r="F97" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B98" t="s">
+        <v>478</v>
+      </c>
+      <c r="C98" t="s">
+        <v>479</v>
+      </c>
+      <c r="D98" t="s">
+        <v>480</v>
+      </c>
+      <c r="E98" t="s">
+        <v>275</v>
+      </c>
+      <c r="F98" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B99" t="s">
+        <v>481</v>
+      </c>
+      <c r="C99" t="s">
+        <v>482</v>
+      </c>
+      <c r="D99" t="s">
+        <v>483</v>
+      </c>
+      <c r="E99" t="s">
+        <v>275</v>
+      </c>
+      <c r="F99" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B100" t="s">
+        <v>484</v>
+      </c>
+      <c r="C100" t="s">
+        <v>485</v>
+      </c>
+      <c r="D100" t="s">
+        <v>486</v>
+      </c>
+      <c r="E100" t="s">
+        <v>275</v>
+      </c>
+      <c r="F100" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B101" t="s">
+        <v>487</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D101" t="s">
+        <v>489</v>
+      </c>
+      <c r="E101" t="s">
+        <v>275</v>
+      </c>
+      <c r="F101" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="B102" t="s">
+        <v>490</v>
+      </c>
+      <c r="C102" t="s">
+        <v>491</v>
+      </c>
+      <c r="D102" t="s">
+        <v>492</v>
+      </c>
+      <c r="E102" t="s">
+        <v>275</v>
+      </c>
+      <c r="F102" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="B103" t="s">
+        <v>493</v>
+      </c>
+      <c r="C103" t="s">
+        <v>494</v>
+      </c>
+      <c r="D103" t="s">
+        <v>495</v>
+      </c>
+      <c r="E103" t="s">
+        <v>275</v>
+      </c>
+      <c r="F103" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B104" t="s">
+        <v>496</v>
+      </c>
+      <c r="C104" t="s">
+        <v>497</v>
+      </c>
+      <c r="D104" t="s">
+        <v>498</v>
+      </c>
+      <c r="E104" t="s">
+        <v>275</v>
+      </c>
+      <c r="F104" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B105" t="s">
+        <v>499</v>
+      </c>
+      <c r="C105" t="s">
+        <v>500</v>
+      </c>
+      <c r="D105" t="s">
+        <v>501</v>
+      </c>
+      <c r="E105" t="s">
+        <v>275</v>
+      </c>
+      <c r="F105" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B106" t="s">
+        <v>502</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D106" t="s">
+        <v>504</v>
+      </c>
+      <c r="E106" t="s">
+        <v>275</v>
+      </c>
+      <c r="F106" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B107" t="s">
+        <v>505</v>
+      </c>
+      <c r="C107" t="s">
+        <v>506</v>
+      </c>
+      <c r="D107" t="s">
+        <v>507</v>
+      </c>
+      <c r="E107" t="s">
+        <v>275</v>
+      </c>
+      <c r="F107" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B108" t="s">
+        <v>508</v>
+      </c>
+      <c r="C108" t="s">
+        <v>509</v>
+      </c>
+      <c r="D108" t="s">
+        <v>510</v>
+      </c>
+      <c r="E108" t="s">
+        <v>276</v>
+      </c>
+      <c r="F108" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+      <c r="B109" t="s">
+        <v>511</v>
+      </c>
+      <c r="C109" t="s">
+        <v>512</v>
+      </c>
+      <c r="D109" t="s">
+        <v>513</v>
+      </c>
+      <c r="E109" t="s">
+        <v>275</v>
+      </c>
+      <c r="F109" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B110" t="s">
+        <v>514</v>
+      </c>
+      <c r="C110" t="s">
+        <v>515</v>
+      </c>
+      <c r="D110" t="s">
+        <v>516</v>
+      </c>
+      <c r="E110" t="s">
+        <v>275</v>
+      </c>
+      <c r="F110" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B111" t="s">
+        <v>517</v>
+      </c>
+      <c r="C111" t="s">
+        <v>518</v>
+      </c>
+      <c r="D111" t="s">
+        <v>519</v>
+      </c>
+      <c r="E111" t="s">
+        <v>275</v>
+      </c>
+      <c r="F111" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B112" t="s">
+        <v>520</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="D112" t="s">
+        <v>522</v>
+      </c>
+      <c r="E112" t="s">
+        <v>275</v>
+      </c>
+      <c r="F112" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B113" t="s">
+        <v>523</v>
+      </c>
+      <c r="C113" t="s">
+        <v>524</v>
+      </c>
+      <c r="D113" t="s">
+        <v>525</v>
+      </c>
+      <c r="E113" t="s">
+        <v>275</v>
+      </c>
+      <c r="F113" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
+      <c r="B114" t="s">
+        <v>526</v>
+      </c>
+      <c r="C114" t="s">
+        <v>527</v>
+      </c>
+      <c r="D114" t="s">
+        <v>528</v>
+      </c>
+      <c r="E114" t="s">
+        <v>275</v>
+      </c>
+      <c r="F114" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
+      <c r="B115" t="s">
+        <v>529</v>
+      </c>
+      <c r="C115" t="s">
+        <v>530</v>
+      </c>
+      <c r="D115" t="s">
+        <v>531</v>
+      </c>
+      <c r="E115" t="s">
+        <v>275</v>
+      </c>
+      <c r="F115" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B116" t="s">
+        <v>532</v>
+      </c>
+      <c r="C116" t="s">
+        <v>533</v>
+      </c>
+      <c r="D116" t="s">
+        <v>534</v>
+      </c>
+      <c r="E116" t="s">
+        <v>275</v>
+      </c>
+      <c r="F116" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B117" t="s">
+        <v>535</v>
+      </c>
+      <c r="C117" t="s">
+        <v>536</v>
+      </c>
+      <c r="D117" t="s">
+        <v>537</v>
+      </c>
+      <c r="E117" t="s">
+        <v>275</v>
+      </c>
+      <c r="F117" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B118" t="s">
+        <v>538</v>
+      </c>
+      <c r="C118" t="s">
+        <v>539</v>
+      </c>
+      <c r="D118" t="s">
+        <v>540</v>
+      </c>
+      <c r="E118" t="s">
+        <v>275</v>
+      </c>
+      <c r="F118" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+      <c r="B119" t="s">
+        <v>541</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D119" t="s">
+        <v>543</v>
+      </c>
+      <c r="E119" t="s">
+        <v>275</v>
+      </c>
+      <c r="F119" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B120" t="s">
+        <v>544</v>
+      </c>
+      <c r="C120" t="s">
+        <v>545</v>
+      </c>
+      <c r="D120" t="s">
+        <v>546</v>
+      </c>
+      <c r="E120" t="s">
+        <v>275</v>
+      </c>
+      <c r="F120" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+      <c r="B121" t="s">
+        <v>547</v>
+      </c>
+      <c r="C121" t="s">
+        <v>548</v>
+      </c>
+      <c r="D121" t="s">
+        <v>549</v>
+      </c>
+      <c r="E121" t="s">
+        <v>275</v>
+      </c>
+      <c r="F121" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+      <c r="B122" t="s">
+        <v>550</v>
+      </c>
+      <c r="C122" t="s">
+        <v>551</v>
+      </c>
+      <c r="D122" t="s">
+        <v>552</v>
+      </c>
+      <c r="E122" t="s">
+        <v>275</v>
+      </c>
+      <c r="F122" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+      <c r="B123" t="s">
+        <v>556</v>
+      </c>
+      <c r="C123" t="s">
+        <v>553</v>
+      </c>
+      <c r="D123" t="s">
+        <v>554</v>
+      </c>
+      <c r="E123" t="s">
+        <v>275</v>
+      </c>
+      <c r="F123" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B124" t="s">
+        <v>555</v>
+      </c>
+      <c r="C124" t="s">
+        <v>557</v>
+      </c>
+      <c r="D124" t="s">
+        <v>558</v>
+      </c>
+      <c r="E124" t="s">
+        <v>275</v>
+      </c>
+      <c r="F124" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
+      <c r="B125" t="s">
+        <v>559</v>
+      </c>
+      <c r="C125" t="s">
+        <v>560</v>
+      </c>
+      <c r="D125" t="s">
+        <v>561</v>
+      </c>
+      <c r="E125" t="s">
+        <v>275</v>
+      </c>
+      <c r="F125" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
+      <c r="B126" t="s">
+        <v>562</v>
+      </c>
+      <c r="C126" t="s">
+        <v>563</v>
+      </c>
+      <c r="D126" t="s">
+        <v>564</v>
+      </c>
+      <c r="E126" t="s">
+        <v>275</v>
+      </c>
+      <c r="F126" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
+      <c r="B127" t="s">
+        <v>565</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D127" t="s">
+        <v>568</v>
+      </c>
+      <c r="E127" t="s">
+        <v>275</v>
+      </c>
+      <c r="F127" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
+      <c r="B128" t="s">
+        <v>569</v>
+      </c>
+      <c r="C128" t="s">
+        <v>570</v>
+      </c>
+      <c r="D128" t="s">
+        <v>571</v>
+      </c>
+      <c r="E128" t="s">
+        <v>275</v>
+      </c>
+      <c r="F128" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
+      <c r="B129" t="s">
+        <v>572</v>
+      </c>
+      <c r="C129" t="s">
+        <v>573</v>
+      </c>
+      <c r="D129" t="s">
+        <v>574</v>
+      </c>
+      <c r="E129" t="s">
+        <v>275</v>
+      </c>
+      <c r="F129" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="B130" t="s">
+        <v>575</v>
+      </c>
+      <c r="C130" t="s">
+        <v>577</v>
+      </c>
+      <c r="D130" t="s">
+        <v>576</v>
+      </c>
+      <c r="E130" t="s">
+        <v>275</v>
+      </c>
+      <c r="F130" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="B131" t="s">
+        <v>567</v>
+      </c>
+      <c r="C131" t="s">
+        <v>578</v>
+      </c>
+      <c r="D131" t="s">
+        <v>579</v>
+      </c>
+      <c r="E131" t="s">
+        <v>275</v>
+      </c>
+      <c r="F131" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="B132" t="s">
+        <v>580</v>
+      </c>
+      <c r="C132" t="s">
+        <v>581</v>
+      </c>
+      <c r="D132" t="s">
+        <v>582</v>
+      </c>
+      <c r="E132" t="s">
+        <v>275</v>
+      </c>
+      <c r="F132" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="B133" t="s">
+        <v>583</v>
+      </c>
+      <c r="C133" t="s">
+        <v>584</v>
+      </c>
+      <c r="D133" t="s">
+        <v>585</v>
+      </c>
+      <c r="E133" t="s">
+        <v>275</v>
+      </c>
+      <c r="F133" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
+      <c r="B134" t="s">
+        <v>586</v>
+      </c>
+      <c r="C134" t="s">
+        <v>587</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="E134" t="s">
+        <v>275</v>
+      </c>
+      <c r="F134" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
+      <c r="B135" t="s">
+        <v>591</v>
+      </c>
+      <c r="C135" t="s">
+        <v>592</v>
+      </c>
+      <c r="D135" t="s">
+        <v>593</v>
+      </c>
+      <c r="E135" t="s">
+        <v>275</v>
+      </c>
+      <c r="F135" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B136" t="s">
+        <v>594</v>
+      </c>
+      <c r="C136" t="s">
+        <v>595</v>
+      </c>
+      <c r="D136" t="s">
+        <v>596</v>
+      </c>
+      <c r="E136" t="s">
+        <v>275</v>
+      </c>
+      <c r="F136" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
+      <c r="B137" t="s">
+        <v>597</v>
+      </c>
+      <c r="C137" t="s">
+        <v>598</v>
+      </c>
+      <c r="D137" t="s">
+        <v>599</v>
+      </c>
+      <c r="E137" t="s">
+        <v>275</v>
+      </c>
+      <c r="F137" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+      <c r="B138" t="s">
+        <v>600</v>
+      </c>
+      <c r="C138" t="s">
+        <v>601</v>
+      </c>
+      <c r="D138" t="s">
+        <v>602</v>
+      </c>
+      <c r="E138" t="s">
+        <v>275</v>
+      </c>
+      <c r="F138" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
+      <c r="B139" t="s">
+        <v>603</v>
+      </c>
+      <c r="C139" t="s">
+        <v>604</v>
+      </c>
+      <c r="D139" t="s">
+        <v>605</v>
+      </c>
+      <c r="E139" t="s">
+        <v>275</v>
+      </c>
+      <c r="F139" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
+      <c r="B140" t="s">
+        <v>606</v>
+      </c>
+      <c r="C140" t="s">
+        <v>607</v>
+      </c>
+      <c r="D140" t="s">
+        <v>608</v>
+      </c>
+      <c r="E140" t="s">
+        <v>275</v>
+      </c>
+      <c r="F140" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
+      <c r="B141" t="s">
+        <v>609</v>
+      </c>
+      <c r="C141" t="s">
+        <v>610</v>
+      </c>
+      <c r="D141" t="s">
+        <v>611</v>
+      </c>
+      <c r="E141" t="s">
+        <v>276</v>
+      </c>
+      <c r="F141" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
+      <c r="B142" t="s">
+        <v>612</v>
+      </c>
+      <c r="C142" t="s">
+        <v>613</v>
+      </c>
+      <c r="D142" t="s">
+        <v>614</v>
+      </c>
+      <c r="E142" t="s">
+        <v>275</v>
+      </c>
+      <c r="F142" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
+      <c r="B143" t="s">
+        <v>589</v>
+      </c>
+      <c r="C143" t="s">
+        <v>616</v>
+      </c>
+      <c r="D143" t="s">
+        <v>617</v>
+      </c>
+      <c r="E143" t="s">
+        <v>275</v>
+      </c>
+      <c r="F143" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
+      <c r="B144" t="s">
+        <v>618</v>
+      </c>
+      <c r="C144" t="s">
+        <v>619</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E144" t="s">
+        <v>275</v>
+      </c>
+      <c r="F144" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
+      <c r="B145" t="s">
+        <v>621</v>
+      </c>
+      <c r="C145" t="s">
+        <v>622</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E145" t="s">
+        <v>275</v>
+      </c>
+      <c r="F145" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
+      <c r="B146" t="s">
+        <v>590</v>
+      </c>
+      <c r="C146" t="s">
+        <v>624</v>
+      </c>
+      <c r="D146" t="s">
+        <v>625</v>
+      </c>
+      <c r="E146" t="s">
+        <v>275</v>
+      </c>
+      <c r="F146" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>615</v>
+      </c>
+      <c r="B147" t="s">
+        <v>626</v>
+      </c>
+      <c r="C147" t="s">
+        <v>627</v>
+      </c>
+      <c r="D147" t="s">
+        <v>628</v>
+      </c>
+      <c r="E147" t="s">
+        <v>276</v>
+      </c>
+      <c r="F147" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
+      <c r="B148" t="s">
+        <v>629</v>
+      </c>
+      <c r="C148" t="s">
+        <v>630</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="E148" t="s">
+        <v>275</v>
+      </c>
+      <c r="F148" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
+      <c r="B149" t="s">
+        <v>632</v>
+      </c>
+      <c r="C149" t="s">
+        <v>633</v>
+      </c>
+      <c r="D149" t="s">
+        <v>634</v>
+      </c>
+      <c r="E149" t="s">
+        <v>275</v>
+      </c>
+      <c r="F149" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
+      <c r="B150" t="s">
+        <v>635</v>
+      </c>
+      <c r="C150" t="s">
+        <v>636</v>
+      </c>
+      <c r="D150" t="s">
+        <v>637</v>
+      </c>
+      <c r="E150" t="s">
+        <v>275</v>
+      </c>
+      <c r="F150" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
+      <c r="B151" t="s">
+        <v>638</v>
+      </c>
+      <c r="C151" t="s">
+        <v>639</v>
+      </c>
+      <c r="D151" t="s">
+        <v>640</v>
+      </c>
+      <c r="E151" t="s">
+        <v>275</v>
+      </c>
+      <c r="F151" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
+      <c r="B152" t="s">
+        <v>641</v>
+      </c>
+      <c r="C152" t="s">
+        <v>642</v>
+      </c>
+      <c r="D152" t="s">
+        <v>643</v>
+      </c>
+      <c r="E152" t="s">
+        <v>275</v>
+      </c>
+      <c r="F152" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
+      <c r="B153" t="s">
+        <v>644</v>
+      </c>
+      <c r="C153" t="s">
+        <v>645</v>
+      </c>
+      <c r="D153" t="s">
+        <v>646</v>
+      </c>
+      <c r="E153" t="s">
+        <v>275</v>
+      </c>
+      <c r="F153" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="B154" t="s">
+        <v>647</v>
+      </c>
+      <c r="C154" t="s">
+        <v>648</v>
+      </c>
+      <c r="D154" t="s">
+        <v>649</v>
+      </c>
+      <c r="E154" t="s">
+        <v>275</v>
+      </c>
+      <c r="F154" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
+      <c r="B155" t="s">
+        <v>650</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="D155" t="s">
+        <v>652</v>
+      </c>
+      <c r="E155" t="s">
+        <v>275</v>
+      </c>
+      <c r="F155" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
+      <c r="B156" t="s">
+        <v>653</v>
+      </c>
+      <c r="C156" t="s">
+        <v>654</v>
+      </c>
+      <c r="D156" t="s">
+        <v>655</v>
+      </c>
+      <c r="E156" t="s">
+        <v>275</v>
+      </c>
+      <c r="F156" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
+      <c r="B157" t="s">
+        <v>656</v>
+      </c>
+      <c r="C157" t="s">
+        <v>657</v>
+      </c>
+      <c r="D157" t="s">
+        <v>658</v>
+      </c>
+      <c r="E157" t="s">
+        <v>275</v>
+      </c>
+      <c r="F157" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
+      <c r="B158" t="s">
+        <v>659</v>
+      </c>
+      <c r="C158" t="s">
+        <v>660</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="E158" t="s">
+        <v>275</v>
+      </c>
+      <c r="F158" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
+      <c r="B159" t="s">
+        <v>662</v>
+      </c>
+      <c r="C159" t="s">
+        <v>663</v>
+      </c>
+      <c r="D159" t="s">
+        <v>664</v>
+      </c>
+      <c r="E159" t="s">
+        <v>275</v>
+      </c>
+      <c r="F159" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
+      <c r="B160" t="s">
+        <v>665</v>
+      </c>
+      <c r="C160" t="s">
+        <v>666</v>
+      </c>
+      <c r="D160" t="s">
+        <v>667</v>
+      </c>
+      <c r="E160" t="s">
+        <v>275</v>
+      </c>
+      <c r="F160" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
+      <c r="B161" t="s">
+        <v>668</v>
+      </c>
+      <c r="C161" t="s">
+        <v>669</v>
+      </c>
+      <c r="D161" t="s">
+        <v>670</v>
+      </c>
+      <c r="E161" t="s">
+        <v>275</v>
+      </c>
+      <c r="F161" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
+      <c r="B162" t="s">
+        <v>671</v>
+      </c>
+      <c r="C162" t="s">
+        <v>672</v>
+      </c>
+      <c r="D162" t="s">
+        <v>673</v>
+      </c>
+      <c r="E162" t="s">
+        <v>275</v>
+      </c>
+      <c r="F162" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+      <c r="B163" t="s">
+        <v>674</v>
+      </c>
+      <c r="C163" t="s">
+        <v>675</v>
+      </c>
+      <c r="D163" t="s">
+        <v>676</v>
+      </c>
+      <c r="E163" t="s">
+        <v>275</v>
+      </c>
+      <c r="F163" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+      <c r="B164" t="s">
+        <v>677</v>
+      </c>
+      <c r="C164" t="s">
+        <v>678</v>
+      </c>
+      <c r="D164" t="s">
+        <v>679</v>
+      </c>
+      <c r="E164" t="s">
+        <v>275</v>
+      </c>
+      <c r="F164" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+      <c r="B165" t="s">
+        <v>680</v>
+      </c>
+      <c r="C165" t="s">
+        <v>681</v>
+      </c>
+      <c r="D165" t="s">
+        <v>682</v>
+      </c>
+      <c r="E165" t="s">
+        <v>275</v>
+      </c>
+      <c r="F165" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>45</v>
+      </c>
+      <c r="B166" t="s">
+        <v>331</v>
+      </c>
+      <c r="C166" t="s">
+        <v>332</v>
+      </c>
+      <c r="D166" t="s">
+        <v>333</v>
+      </c>
+      <c r="E166" t="s">
+        <v>275</v>
+      </c>
+      <c r="F166" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+      <c r="B167" t="s">
+        <v>683</v>
+      </c>
+      <c r="C167" t="s">
+        <v>684</v>
+      </c>
+      <c r="D167" t="s">
+        <v>685</v>
+      </c>
+      <c r="E167" t="s">
+        <v>275</v>
+      </c>
+      <c r="F167" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+      <c r="B168" t="s">
+        <v>686</v>
+      </c>
+      <c r="C168" t="s">
+        <v>687</v>
+      </c>
+      <c r="D168" t="s">
+        <v>688</v>
+      </c>
+      <c r="E168" t="s">
+        <v>275</v>
+      </c>
+      <c r="F168" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+      <c r="B169" t="s">
+        <v>689</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D169" t="s">
+        <v>691</v>
+      </c>
+      <c r="E169" t="s">
+        <v>275</v>
+      </c>
+      <c r="F169" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+      <c r="B170" t="s">
+        <v>692</v>
+      </c>
+      <c r="C170" t="s">
+        <v>693</v>
+      </c>
+      <c r="D170" t="s">
+        <v>694</v>
+      </c>
+      <c r="E170" t="s">
+        <v>275</v>
+      </c>
+      <c r="F170" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+      <c r="B171" t="s">
+        <v>695</v>
+      </c>
+      <c r="C171" t="s">
+        <v>696</v>
+      </c>
+      <c r="D171" t="s">
+        <v>697</v>
+      </c>
+      <c r="E171" t="s">
+        <v>275</v>
+      </c>
+      <c r="F171" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+      <c r="B172" t="s">
+        <v>698</v>
+      </c>
+      <c r="C172" t="s">
+        <v>699</v>
+      </c>
+      <c r="D172" t="s">
+        <v>700</v>
+      </c>
+      <c r="E172" t="s">
+        <v>275</v>
+      </c>
+      <c r="F172" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+      <c r="B173" t="s">
+        <v>701</v>
+      </c>
+      <c r="C173" t="s">
+        <v>702</v>
+      </c>
+      <c r="D173" t="s">
+        <v>703</v>
+      </c>
+      <c r="E173" t="s">
+        <v>276</v>
+      </c>
+      <c r="F173" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+      <c r="B174" t="s">
+        <v>704</v>
+      </c>
+      <c r="C174" t="s">
+        <v>705</v>
+      </c>
+      <c r="D174" t="s">
+        <v>706</v>
+      </c>
+      <c r="E174" t="s">
+        <v>276</v>
+      </c>
+      <c r="F174" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+      <c r="B175" t="s">
+        <v>707</v>
+      </c>
+      <c r="C175" t="s">
+        <v>708</v>
+      </c>
+      <c r="D175" t="s">
+        <v>709</v>
+      </c>
+      <c r="E175" t="s">
+        <v>275</v>
+      </c>
+      <c r="F175" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+      <c r="B176" t="s">
+        <v>710</v>
+      </c>
+      <c r="C176" t="s">
+        <v>711</v>
+      </c>
+      <c r="D176" t="s">
+        <v>712</v>
+      </c>
+      <c r="E176" t="s">
+        <v>276</v>
+      </c>
+      <c r="F176" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+      <c r="B177" t="s">
+        <v>713</v>
+      </c>
+      <c r="C177" t="s">
+        <v>714</v>
+      </c>
+      <c r="D177" t="s">
+        <v>715</v>
+      </c>
+      <c r="E177" t="s">
+        <v>275</v>
+      </c>
+      <c r="F177" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
+      <c r="B178" t="s">
+        <v>716</v>
+      </c>
+      <c r="C178" t="s">
+        <v>717</v>
+      </c>
+      <c r="D178" t="s">
+        <v>718</v>
+      </c>
+      <c r="E178" t="s">
+        <v>275</v>
+      </c>
+      <c r="F178" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
+      <c r="B179" t="s">
+        <v>719</v>
+      </c>
+      <c r="C179" t="s">
+        <v>720</v>
+      </c>
+      <c r="D179" t="s">
+        <v>721</v>
+      </c>
+      <c r="E179" t="s">
+        <v>275</v>
+      </c>
+      <c r="F179" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+      <c r="B180" t="s">
+        <v>722</v>
+      </c>
+      <c r="C180" t="s">
+        <v>723</v>
+      </c>
+      <c r="D180" t="s">
+        <v>724</v>
+      </c>
+      <c r="E180" t="s">
+        <v>275</v>
+      </c>
+      <c r="F180" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="B181" t="s">
+        <v>725</v>
+      </c>
+      <c r="C181" t="s">
+        <v>726</v>
+      </c>
+      <c r="D181" t="s">
+        <v>727</v>
+      </c>
+      <c r="E181" t="s">
+        <v>275</v>
+      </c>
+      <c r="F181" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
+      <c r="B182" t="s">
+        <v>728</v>
+      </c>
+      <c r="C182" t="s">
+        <v>729</v>
+      </c>
+      <c r="D182" t="s">
+        <v>730</v>
+      </c>
+      <c r="E182" t="s">
+        <v>276</v>
+      </c>
+      <c r="F182" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
+      <c r="B183" t="s">
+        <v>731</v>
+      </c>
+      <c r="C183" t="s">
+        <v>732</v>
+      </c>
+      <c r="D183" t="s">
+        <v>733</v>
+      </c>
+      <c r="E183" t="s">
+        <v>275</v>
+      </c>
+      <c r="F183" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
+      <c r="B184" t="s">
+        <v>734</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D184" t="s">
+        <v>736</v>
+      </c>
+      <c r="E184" t="s">
+        <v>275</v>
+      </c>
+      <c r="F184" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+      <c r="B185" t="s">
+        <v>737</v>
+      </c>
+      <c r="C185" t="s">
+        <v>738</v>
+      </c>
+      <c r="D185" t="s">
+        <v>739</v>
+      </c>
+      <c r="E185" t="s">
+        <v>275</v>
+      </c>
+      <c r="F185" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="B186" t="s">
+        <v>740</v>
+      </c>
+      <c r="C186" t="s">
+        <v>741</v>
+      </c>
+      <c r="D186" t="s">
+        <v>742</v>
+      </c>
+      <c r="E186" t="s">
+        <v>275</v>
+      </c>
+      <c r="F186" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>197</v>
+      <c r="B187" t="s">
+        <v>743</v>
+      </c>
+      <c r="C187" t="s">
+        <v>744</v>
+      </c>
+      <c r="D187" t="s">
+        <v>745</v>
+      </c>
+      <c r="E187" t="s">
+        <v>275</v>
+      </c>
+      <c r="F187" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{0C3DB127-BABD-4406-8397-AF94CA7185E8}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{BC4F8AFD-D5AB-477D-872E-EE31DBEF5072}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{4CAE91A9-4647-4510-AEDF-15B874BF341E}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{F40A887E-B3A8-4618-AED1-98408267BBF8}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{5A2BD9A9-6D62-40B5-AD0A-E3FDD8E822D6}"/>
+    <hyperlink ref="D8" r:id="rId6" xr:uid="{0ABA22DA-0F94-436D-86DF-CDDC36474110}"/>
+    <hyperlink ref="D15" r:id="rId7" xr:uid="{787CB512-FA2C-4AF2-B5EB-A8C0C080B9F8}"/>
+    <hyperlink ref="D24" r:id="rId8" xr:uid="{4A7BED6A-DB6B-4D6B-9466-465E9AB3FECF}"/>
+    <hyperlink ref="C34" r:id="rId9" xr:uid="{DDB77DCE-4E34-4F08-97C8-E08503ED25E8}"/>
+    <hyperlink ref="D44" r:id="rId10" xr:uid="{DBFFDEBD-F0BA-4E39-9EC9-9E85C8AE504C}"/>
+    <hyperlink ref="C62" r:id="rId11" xr:uid="{E05598BE-B145-44D0-B569-E2CE3024D19F}"/>
+    <hyperlink ref="C74" r:id="rId12" xr:uid="{64627544-26EF-43AD-B315-AD667E0E5356}"/>
+    <hyperlink ref="C82" r:id="rId13" xr:uid="{2C07E87D-A912-4334-AA8B-9FCE9C12790E}"/>
+    <hyperlink ref="C97" r:id="rId14" xr:uid="{FA50154D-5662-45DD-8864-68CFC15FCDE8}"/>
+    <hyperlink ref="C101" r:id="rId15" xr:uid="{894C4091-CFB1-45CC-A88C-E4D0386188D3}"/>
+    <hyperlink ref="C106" r:id="rId16" xr:uid="{2BF09282-BAA1-4AC8-8727-FD731171C3DD}"/>
+    <hyperlink ref="C112" r:id="rId17" xr:uid="{A1C626C1-3C1A-43FD-B784-E19D671AEBF7}"/>
+    <hyperlink ref="C119" r:id="rId18" xr:uid="{4D0119B0-82EF-49FB-B8A4-115C84DA8488}"/>
+    <hyperlink ref="C127" r:id="rId19" xr:uid="{F4513D4D-AA76-4EEE-8B1B-1778C5838CB1}"/>
+    <hyperlink ref="D134" r:id="rId20" xr:uid="{1A443407-6C9E-45A5-ABE5-B27F5B6D1669}"/>
+    <hyperlink ref="D144" r:id="rId21" xr:uid="{B6BD44E1-D452-4F1B-B03E-50F93533C19E}"/>
+    <hyperlink ref="D145" r:id="rId22" xr:uid="{F4D2EB08-696C-4117-8114-9C77374F4F08}"/>
+    <hyperlink ref="D148" r:id="rId23" xr:uid="{A5264515-2E5E-4F92-8E1A-7AFFF447B4AA}"/>
+    <hyperlink ref="C155" r:id="rId24" xr:uid="{67B6485C-E914-4A77-B7E0-3181CDAB79E9}"/>
+    <hyperlink ref="D158" r:id="rId25" xr:uid="{119EAB0F-164F-4A00-9893-2C5F856E6C3C}"/>
+    <hyperlink ref="C169" r:id="rId26" xr:uid="{6EBC1EAE-4786-4E99-BD2F-DE3880A069E5}"/>
+    <hyperlink ref="C184" r:id="rId27" xr:uid="{689096C5-620B-4EC5-A434-C3ED62189762}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>